--- a/codebook/codebook_sorted.xlsx
+++ b/codebook/codebook_sorted.xlsx
@@ -369,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
@@ -778,25 +778,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>gender</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Gender</t>
-        </is>
+          <t>sex_num</t>
+        </is>
+      </c>
+      <c r="C13" t="e">
+        <v>#N/A</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>fct</t>
+          <t>dbl</t>
         </is>
       </c>
       <c r="E13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Man (including Trans Male/Trans Man), Non-binary (would like to give more detail), Woman (including Trans Female/Trans Woman)</t>
+          <t/>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -811,12 +809,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ethnicity_simplified</t>
+          <t>gender</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethnicity, simplified</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -829,7 +827,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian, Black, Mixed, Other, White</t>
+          <t>Man (including Trans Male/Trans Man), Non-binary (would like to give more detail), Woman (including Trans Female/Trans Woman)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -844,25 +842,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>household_income_usd_us_participants_only</t>
+          <t>ethnicity_simplified</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Household income (USD; U.S. participants only)</t>
+          <t>Ethnicity, simplified</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ord</t>
+          <t>fct</t>
         </is>
       </c>
       <c r="E15">
-        <v>95</v>
+        <v>6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Less than $10000, $10000–$15999, $16000–$19999, $20000–$24999, $25000–$29999, $30000–$34999, $35000–$39999, $40000–$49999, $50000–$59999, $60000–$74999, $75000–$99999, $100000–$149999, More than $150000</t>
+          <t>Asian, Black, Mixed, Other, White</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -877,12 +875,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>personal_income_usd_us_participants_only</t>
+          <t>household_income_usd_us_participants_only</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Personal income (USD; U.S. participants only)</t>
+          <t>Household income (USD; U.S. participants only)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -891,11 +889,11 @@
         </is>
       </c>
       <c r="E16">
-        <v>230</v>
+        <v>95</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Less than $10000, $10000–$15999, $16000–$19999, $20000–$24999, $25000–$29999, $30000–$34999, $35000–$39999, $40000–$49999, $50000–$59999, $60000–$74999, $75000–$99999, $100000–$149999, More than $150000, Rather not say</t>
+          <t>Less than $10000, $10000–$15999, $16000–$19999, $20000–$24999, $25000–$29999, $30000–$34999, $35000–$39999, $40000–$49999, $50000–$59999, $60000–$74999, $75000–$99999, $100000–$149999, More than $150000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -910,25 +908,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>highest_level_of_education_completed_by_parents</t>
+          <t>personal_income_usd_us_participants_only</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Highest level of education completed by parents</t>
+          <t>Personal income (USD; U.S. participants only)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>fct</t>
+          <t>ord</t>
         </is>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>230</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>No formal qualifications, Secondary education (e.g. GED/GCSE), High school diploma / A-Levels / Community college, Undergraduate degree (BA/BSc/Other), Graduate degree (MA,MSc/MPhil/Other), Doctorate degree (PhD/other), Don't know, Not applicable / Prefer not to say</t>
+          <t>Less than $10000, $10000–$15999, $16000–$19999, $20000–$24999, $25000–$29999, $30000–$34999, $35000–$39999, $40000–$49999, $50000–$59999, $60000–$74999, $75000–$99999, $100000–$149999, More than $150000, Rather not say</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -943,12 +941,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>undergraduate_year_of_study</t>
+          <t>highest_level_of_education_completed_by_parents</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Undergraduate year of study</t>
+          <t>Highest level of education completed by parents</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -957,11 +955,11 @@
         </is>
       </c>
       <c r="E18">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1st Year, 2nd Year, 3rd Year, 4th Year, Other</t>
+          <t>No formal qualifications, Secondary education (e.g. GED/GCSE), High school diploma / A-Levels / Community college, Undergraduate degree (BA/BSc/Other), Graduate degree (MA,MSc/MPhil/Other), Doctorate degree (PhD/other), Don't know, Not applicable / Prefer not to say</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -976,12 +974,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>student_status</t>
+          <t>undergraduate_year_of_study</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Student status</t>
+          <t>Undergraduate year of study</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -990,11 +988,11 @@
         </is>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>DATA_EXPIRED, No, Yes</t>
+          <t>1st Year, 2nd Year, 3rd Year, 4th Year, Other</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1009,12 +1007,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>employment_status</t>
+          <t>student_status</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Employment status</t>
+          <t>Student status</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1027,7 +1025,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Due to start a new job within the next month, Full-Time, Not in paid work (e.g. homemaker', 'retired or disabled), Other, Part-Time, Unemployed (and job seeking)</t>
+          <t>DATA_EXPIRED, No, Yes</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1042,12 +1040,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>country_of_residence</t>
+          <t>employment_status</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Country of residence</t>
+          <t>Employment status</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1060,7 +1058,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Due to start a new job within the next month, Full-Time, Not in paid work (e.g. homemaker', 'retired or disabled), Other, Part-Time, Unemployed (and job seeking)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1075,12 +1073,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>country_of_birth</t>
+          <t>country_of_residence</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Country of birth</t>
+          <t>Country of residence</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1093,7 +1091,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brazil, Canada, China, Colombia, Cuba, Dominican Republic, Guyana, Haiti, Jordan, Kenya, Mexico, Nigeria, Saudi Arabia, Turkey, United Kingdom, United States, United States Minor Outlying Islands</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1108,12 +1106,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nationality</t>
+          <t>country_of_birth</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nationality</t>
+          <t>Country of birth</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1126,7 +1124,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brazil, China, Colombia, Cuba, Dominican Republic, Germany, Guyana, Haiti, Iran, Italy, Japan, Mexico, Nigeria, Puerto Rico, Turkey, United Kingdom, United States</t>
+          <t>Brazil, Canada, China, Colombia, Cuba, Dominican Republic, Guyana, Haiti, Jordan, Kenya, Mexico, Nigeria, Saudi Arabia, Turkey, United Kingdom, United States, United States Minor Outlying Islands</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1141,12 +1139,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>nationality</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Primary language</t>
+          <t>Nationality</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1159,7 +1157,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arabic, Cantonese, Chinese, English, French, Japanese, Mandarin, Portuguese, Romanian, Russian, Serbian, Spanish, Swahili, Turkish, Urdu</t>
+          <t>Brazil, China, Colombia, Cuba, Dominican Republic, Germany, Guyana, Haiti, Iran, Italy, Japan, Mexico, Nigeria, Puerto Rico, Turkey, United Kingdom, United States</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1174,12 +1172,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>fluent_languages</t>
+          <t>language</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fluent languages</t>
+          <t>Primary language</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1192,7 +1190,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arabic, English, Cantonese, English, Mandarin, Chinese, English, Chinese, English, Mandarin, Somali, Swahili, English, English, Arabic, English, Bengali, English, Chinese, English, French, English, German, English, Hungarian, English, Mandarin, English, Other, English, Portuguese, English, Russian, English, Spanish, English, Swahili, English, Urdu, Farsi, English, Japanese, English, Spanish, Korean, English, Portuguese, English, Romanian, Spanish, English, Russian, Ukrainian, English, Spanish, English, Telugu, English</t>
+          <t>Arabic, Cantonese, Chinese, English, French, Japanese, Mandarin, Portuguese, Romanian, Russian, Serbian, Spanish, Swahili, Turkish, Urdu</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1207,15 +1205,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>n_fluent_languages</t>
-        </is>
-      </c>
-      <c r="C26" t="e">
-        <v>#N/A</v>
+          <t>fluent_languages</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Fluent languages</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>fct</t>
         </is>
       </c>
       <c r="E26">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t/>
+          <t>Arabic, English, Cantonese, English, Mandarin, Chinese, English, Chinese, English, Mandarin, Somali, Swahili, English, English, Arabic, English, Bengali, English, Chinese, English, French, English, German, English, Hungarian, English, Mandarin, English, Other, English, Portuguese, English, Russian, English, Spanish, English, Swahili, English, Urdu, Farsi, English, Japanese, English, Spanish, Korean, English, Portuguese, English, Romanian, Spanish, English, Russian, Ukrainian, English, Spanish, English, Telugu, English</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>multilingual</t>
+          <t>n_fluent_languages</t>
         </is>
       </c>
       <c r="C27" t="e">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>fct</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E27">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>One language, Multiple languages</t>
+          <t/>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1269,13 +1269,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>current_u_s_state_of_residence</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Current U.S. state of residence</t>
-        </is>
+          <t>multilingual</t>
+        </is>
+      </c>
+      <c r="C28" t="e">
+        <v>#N/A</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1287,7 +1285,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alabama (AL), Arizona (AZ), Arkansas (AR), California (CA), Colorado (CO), Connecticut (CT), Delaware (DE), Florida (FL), Georgia (GA), Hawaii (HI), Idaho (ID), Illinois (IL), Indiana (IN), Iowa (IA), Kansas (KS), Kentucky (KY), Louisiana (LA), Maryland (MD), Massachusetts (MA), Michigan (MI), Minnesota (MN), Mississippi (MS), Missouri (MO), Nevada (NV), New Jersey (NJ), New York (NY), North Carolina (NC), Ohio (OH), Oklahoma (OK), Oregon (OR), Pennsylvania (PA), Rhode Island (RI), South Carolina (SC), Tennessee (TN), Texas (TX), Virginia (VA), Washington (WA), Wisconsin (WI), Wyoming (WY)</t>
+          <t>One language, Multiple languages</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1302,12 +1300,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>relationship_marital_status</t>
+          <t>current_u_s_state_of_residence</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Relationship or marital status</t>
+          <t>Current U.S. state of residence</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1320,7 +1318,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Divorced, Engaged, In a relationship, Married, Never married, Single</t>
+          <t>Alabama (AL), Arizona (AZ), Arkansas (AR), California (CA), Colorado (CO), Connecticut (CT), Delaware (DE), Florida (FL), Georgia (GA), Hawaii (HI), Idaho (ID), Illinois (IL), Indiana (IN), Iowa (IA), Kansas (KS), Kentucky (KY), Louisiana (LA), Maryland (MD), Massachusetts (MA), Michigan (MI), Minnesota (MN), Mississippi (MS), Missouri (MO), Nevada (NV), New Jersey (NJ), New York (NY), North Carolina (NC), Ohio (OH), Oklahoma (OK), Oregon (OR), Pennsylvania (PA), Rhode Island (RI), South Carolina (SC), Tennessee (TN), Texas (TX), Virginia (VA), Washington (WA), Wisconsin (WI), Wyoming (WY)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1335,31 +1333,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>q7_3_1</t>
+          <t>relationship_marital_status</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CHURCH'S PUBLIC LETTER
-[% of Graves excluded]       Clue - [25%]   The grave is not located in the northwestern part of the cemetery</t>
+          <t>Relationship or marital status</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>dbl+lbl</t>
+          <t>fct</t>
         </is>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t/>
+          <t>Divorced, Engaged, In a relationship, Married, Never married, Single</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2, 1, 3</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -1369,13 +1366,13 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>q7_3_2</t>
+          <t>q7_3_1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
           <t>CHURCH'S PUBLIC LETTER
-[% of Graves excluded]       Clue - [25%]   The person buried there died before 1776</t>
+[% of Graves excluded]       Clue - [25%]   The grave is not located in the northwestern part of the cemetery</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1403,13 +1400,13 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>q7_3_3</t>
+          <t>q7_3_2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
           <t>CHURCH'S PUBLIC LETTER
-[% of Graves excluded]       Clue - [25%]   The person buried there did not die in autumn</t>
+[% of Graves excluded]       Clue - [25%]   The person buried there died before 1776</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1437,13 +1434,13 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>q7_3_4</t>
+          <t>q7_3_3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
           <t>CHURCH'S PUBLIC LETTER
-[% of Graves excluded]       Clue - [25%]   The tombstone does not have any religious symbols, nature symbols, or images engraved on it</t>
+[% of Graves excluded]       Clue - [25%]   The person buried there did not die in autumn</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1471,13 +1468,13 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>q7_3_5</t>
+          <t>q7_3_4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
           <t>CHURCH'S PUBLIC LETTER
-[% of Graves excluded]       Clue - [25%]   The inscription does not include “beloved father” on it</t>
+[% of Graves excluded]       Clue - [25%]   The tombstone does not have any religious symbols, nature symbols, or images engraved on it</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1505,13 +1502,13 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>q7_3_6</t>
+          <t>q7_3_5</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
           <t>CHURCH'S PUBLIC LETTER
-[% of Graves excluded]       Clue - [1%]    The person buried there lived fewer than 100 years</t>
+[% of Graves excluded]       Clue - [25%]   The inscription does not include “beloved father” on it</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1539,13 +1536,13 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>q7_3_7</t>
+          <t>q7_3_6</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
           <t>CHURCH'S PUBLIC LETTER
-[% of Graves excluded]       Clue - [1%]    The person buried there died of natural causes</t>
+[% of Graves excluded]       Clue - [1%]    The person buried there lived fewer than 100 years</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1573,13 +1570,13 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>q7_3_8</t>
+          <t>q7_3_7</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
           <t>CHURCH'S PUBLIC LETTER
-[% of Graves excluded]       Clue - [1%]    The person buried there was a monk</t>
+[% of Graves excluded]       Clue - [1%]    The person buried there died of natural causes</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1607,13 +1604,13 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>q7_3_9</t>
+          <t>q7_3_8</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
           <t>CHURCH'S PUBLIC LETTER
-[% of Graves excluded]       Clue - [1%]    The tombstone does not involve a statue</t>
+[% of Graves excluded]       Clue - [1%]    The person buried there was a monk</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1641,13 +1638,13 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>q7_3_10</t>
+          <t>q7_3_9</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
           <t>CHURCH'S PUBLIC LETTER
-[% of Graves excluded]       Clue - [1%]    The grave is not located within 50 yards of the current grounds keepers shed</t>
+[% of Graves excluded]       Clue - [1%]    The tombstone does not involve a statue</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1675,13 +1672,13 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>q7_4_1</t>
+          <t>q7_3_10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ONLY [Field-which%20letter]
-[% of Graves excluded]       Clue - [25%]   The name of the person ends in "-us"</t>
+          <t>CHURCH'S PUBLIC LETTER
+[% of Graves excluded]       Clue - [1%]    The grave is not located within 50 yards of the current grounds keepers shed</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1709,13 +1706,13 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>q7_4_2</t>
+          <t>q7_4_1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
           <t>ONLY [Field-which%20letter]
-[% of Graves excluded]       Clue - [25%]   The person buried there was not an orphan</t>
+[% of Graves excluded]       Clue - [25%]   The name of the person ends in "-us"</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1743,13 +1740,13 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>q7_4_3</t>
+          <t>q7_4_2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
           <t>ONLY [Field-which%20letter]
-[% of Graves excluded]       Clue - [25%]   The grave is not on the hill of the cemetery</t>
+[% of Graves excluded]       Clue - [25%]   The person buried there was not an orphan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1777,13 +1774,13 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>q7_4_4</t>
+          <t>q7_4_3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
           <t>ONLY [Field-which%20letter]
-[% of Graves excluded]       Clue - [25%]   The person buried there was not born in springtime</t>
+[% of Graves excluded]       Clue - [25%]   The grave is not on the hill of the cemetery</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1811,13 +1808,13 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>q7_4_5</t>
+          <t>q7_4_4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
           <t>ONLY [Field-which%20letter]
-[% of Graves excluded]       Clue - [25%]   The grave is not located in the southeastern part of the cemetery</t>
+[% of Graves excluded]       Clue - [25%]   The person buried there was not born in springtime</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1845,13 +1842,13 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>q7_4_6</t>
+          <t>q7_4_5</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
           <t>ONLY [Field-which%20letter]
-[% of Graves excluded]       Clue - [1%]    The person is not buried a mausoleum</t>
+[% of Graves excluded]       Clue - [25%]   The grave is not located in the southeastern part of the cemetery</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1879,13 +1876,13 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>q7_4_7</t>
+          <t>q7_4_6</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
           <t>ONLY [Field-which%20letter]
-[% of Graves excluded]       Clue - [1%]    The tombstone includes the person's first name, last name, and date of death</t>
+[% of Graves excluded]       Clue - [1%]    The person is not buried a mausoleum</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1913,13 +1910,13 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>q7_4_8</t>
+          <t>q7_4_7</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
           <t>ONLY [Field-which%20letter]
-[% of Graves excluded]       Clue - [1%]    The grave is not located next to the old oak tree</t>
+[% of Graves excluded]       Clue - [1%]    The tombstone includes the person's first name, last name, and date of death</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1947,13 +1944,13 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>q7_4_9</t>
+          <t>q7_4_8</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
           <t>ONLY [Field-which%20letter]
-[% of Graves excluded]       Clue - [1%]    The treasure is not in grave 84, 85, 86, or 87</t>
+[% of Graves excluded]       Clue - [1%]    The grave is not located next to the old oak tree</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1981,13 +1978,13 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>q7_4_10</t>
+          <t>q7_4_9</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
           <t>ONLY [Field-which%20letter]
-[% of Graves excluded]       Clue - [1%]    The tombstone is made of white marble</t>
+[% of Graves excluded]       Clue - [1%]    The treasure is not in grave 84, 85, 86, or 87</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2015,12 +2012,13 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>q9_1_1</t>
+          <t>q7_4_10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>STRATEGIES - I did not think much about what I shared.</t>
+          <t>ONLY [Field-which%20letter]
+[% of Graves excluded]       Clue - [1%]    The tombstone is made of white marble</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2029,7 +2027,7 @@
         </is>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2038,7 +2036,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1, 2, 3, 4, 5</t>
+          <t>2, 1, 3</t>
         </is>
       </c>
     </row>
@@ -2048,12 +2046,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>q9_1_2</t>
+          <t>q9_1_1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>STRATEGIES - I shared what I thought was interesting.</t>
+          <t>STRATEGIES - I did not think much about what I shared.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2081,12 +2079,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>q9_1_3</t>
+          <t>q9_1_2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>STRATEGIES - I just shared everything.</t>
+          <t>STRATEGIES - I shared what I thought was interesting.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2114,12 +2112,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>q9_1_4</t>
+          <t>q9_1_3</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>STRATEGIES - I tried to share very little information.</t>
+          <t>STRATEGIES - I just shared everything.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2147,12 +2145,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>q9_1_5</t>
+          <t>q9_1_4</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>STRATEGIES - I tried to share as much information as possible.</t>
+          <t>STRATEGIES - I tried to share very little information.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2180,12 +2178,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>q9_1_6</t>
+          <t>q9_1_5</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>STRATEGIES - I tried to share information that ruled out more graves.</t>
+          <t>STRATEGIES - I tried to share as much information as possible.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2213,12 +2211,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>q9_1_7</t>
+          <t>q9_1_6</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>STRATEGIES - I focused more on sharing information that ruled out fewer graves.</t>
+          <t>STRATEGIES - I tried to share information that ruled out more graves.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2246,12 +2244,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>q9_1_8</t>
+          <t>q9_1_7</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>STRATEGIES - I focused on sharing information that everyone already had access to.</t>
+          <t>STRATEGIES - I focused more on sharing information that ruled out fewer graves.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2279,12 +2277,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>q9_1_9</t>
+          <t>q9_1_8</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>STRATEGIES - I tried to share information that others likely did not know yet.</t>
+          <t>STRATEGIES - I focused on sharing information that everyone already had access to.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2312,12 +2310,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>q9_1_10</t>
+          <t>q9_1_9</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>STRATEGIES - I tried to share information that ruled out more graves and others did not know.</t>
+          <t>STRATEGIES - I tried to share information that others likely did not know yet.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2345,12 +2343,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>q9_1_11</t>
+          <t>q9_1_10</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>STRATEGIES - I tried to share information that ruled out fewer graves and others did not know.</t>
+          <t>STRATEGIES - I tried to share information that ruled out more graves and others did not know.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2378,12 +2376,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>q9_1_12</t>
+          <t>q9_1_11</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>STRATEGIES - I tried to share information that ruled out more graves and others already knew.</t>
+          <t>STRATEGIES - I tried to share information that ruled out fewer graves and others did not know.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2411,12 +2409,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>q9_1_13</t>
+          <t>q9_1_12</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>STRATEGIES - I tried to share information that ruled out fewer graves and others already knew.</t>
+          <t>STRATEGIES - I tried to share information that ruled out more graves and others already knew.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2444,21 +2442,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>need_cog_n_answered</t>
+          <t>q9_1_13</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Need for Cognition items answered</t>
+          <t>STRATEGIES - I tried to share information that ruled out fewer graves and others already knew.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>dbl</t>
+          <t>dbl+lbl</t>
         </is>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2467,7 +2465,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t/>
+          <t>1, 2, 3, 4, 5</t>
         </is>
       </c>
     </row>
@@ -2477,12 +2475,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>need_cog_mean</t>
+          <t>need_cog_n_answered</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Need for Cognition mean score</t>
+          <t>Need for Cognition items answered</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2491,7 +2489,7 @@
         </is>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2510,12 +2508,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>dirty_dozen_narcissism_n</t>
+          <t>need_cog_mean</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dirty Dozen Narcissism items answered</t>
+          <t>Need for Cognition mean score</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2524,7 +2522,7 @@
         </is>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2543,12 +2541,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>dirty_dozen_psychopathy_n</t>
+          <t>dirty_dozen_narcissism_n</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dirty Dozen Psychopathy items answered</t>
+          <t>Dirty Dozen Narcissism items answered</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2576,12 +2574,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>dirty_dozen_machiavellianism_n</t>
+          <t>dirty_dozen_psychopathy_n</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dirty Dozen Machiavellianism items answered</t>
+          <t>Dirty Dozen Psychopathy items answered</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2609,12 +2607,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>dirty_dozen_narcissism</t>
+          <t>dirty_dozen_machiavellianism_n</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dirty Dozen Narcissism mean score</t>
+          <t>Dirty Dozen Machiavellianism items answered</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2623,7 +2621,7 @@
         </is>
       </c>
       <c r="E68">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2642,12 +2640,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>dirty_dozen_psychopathy</t>
+          <t>dirty_dozen_narcissism</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dirty Dozen Psychopathy mean score</t>
+          <t>Dirty Dozen Narcissism mean score</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2675,12 +2673,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>dirty_dozen_machiavellianism</t>
+          <t>dirty_dozen_psychopathy</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dirty Dozen Machiavellianism mean score</t>
+          <t>Dirty Dozen Psychopathy mean score</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2708,12 +2706,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>cooperation_n_answered</t>
+          <t>dirty_dozen_machiavellianism</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cooperation items answered</t>
+          <t>Dirty Dozen Machiavellianism mean score</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2722,7 +2720,7 @@
         </is>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2741,12 +2739,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>cooperation_mean</t>
+          <t>cooperation_n_answered</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cooperation mean score</t>
+          <t>Cooperation items answered</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2755,7 +2753,7 @@
         </is>
       </c>
       <c r="E72">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2774,22 +2772,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>q14_2</t>
+          <t>cooperation_mean</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Please let us know if you have feedback on this project.
-For example, what issues, if any, did you have any issues completing the survey? Which questions or instructions, if any, did you find confusing or unclear? If you experienced technical problems, please describe.</t>
+          <t>Cooperation mean score</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>chr</t>
+          <t>dbl</t>
         </is>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2808,17 +2805,18 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>recorded_date</t>
+          <t>q14_2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Recorded Date</t>
+          <t>Please let us know if you have feedback on this project.
+For example, what issues, if any, did you have any issues completing the survey? Which questions or instructions, if any, did you find confusing or unclear? If you experienced technical problems, please describe.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>dttm</t>
+          <t>chr</t>
         </is>
       </c>
       <c r="E74">
@@ -2841,17 +2839,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>progress</t>
+          <t>recorded_date</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Recorded Date</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>dbl</t>
+          <t>dttm</t>
         </is>
       </c>
       <c r="E75">
@@ -2874,12 +2872,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>duration_in_seconds</t>
+          <t>progress</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Duration (in seconds)</t>
+          <t>Progress</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2907,7 +2905,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>duration_min</t>
+          <t>duration_in_seconds</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2940,12 +2938,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>time_taken</t>
+          <t>duration_min</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Prolific time taken</t>
+          <t>Duration (in seconds)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2954,7 +2952,7 @@
         </is>
       </c>
       <c r="E78">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2973,17 +2971,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>completion_code</t>
+          <t>time_taken</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Prolific completion code</t>
+          <t>Prolific time taken</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>chr</t>
+          <t>dbl</t>
         </is>
       </c>
       <c r="E79">
@@ -3006,17 +3004,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>total_approvals</t>
+          <t>completion_code</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Total Prolific approvals</t>
+          <t>Prolific completion code</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>dbl</t>
+          <t>chr</t>
         </is>
       </c>
       <c r="E80">
@@ -3028,6 +3026,39 @@
         </is>
       </c>
       <c r="G80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>total_approvals</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Total Prolific approvals</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>dbl</t>
+        </is>
+      </c>
+      <c r="E81">
+        <v>3</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t/>
         </is>
